--- a/testing/kertas-kerja/kertas-kerja-sederhana.xlsx
+++ b/testing/kertas-kerja/kertas-kerja-sederhana.xlsx
@@ -540,12 +540,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="96" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -702,222 +703,349 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Semua tombol bisa dipakai pakai keyboard saja</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Yang diperiksa</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
+          <t>Semua tombol bisa dipakai pakai keyboard saja</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Keyboard saja (Tab, Shift+Tab, Enter, Spasi, Esc, tombol panah). Tetikus tidak dipakai.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
+          <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Keyboard saja + perekam layar (Windows: Win+Alt+R)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
+          <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Keyboard + DevTools: klik kanan elemen, pilih Inspect</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Ada tombol lompat langsung ke konten utama</t>
+          <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Perekam layar + DevTools tab Accessibility</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Hanya ada satu bagian header di halaman</t>
+          <t>Ada tombol lompat langsung ke konten utama</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Keyboard saja. Tekan Tab sekali di awal halaman.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Ada tepat satu judul utama (h1)</t>
+          <t>Hanya ada satu bagian header di halaman</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>NVDA: tekan NVDA+Insert+F7, pilih bagian Landmarks, hitung jumper banner</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Urutan judul tidak melompat-lompat</t>
+          <t>Ada tepat satu judul utama (h1)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>DevTools: ketik document.querySelectorAll('h1').length di Console, atau NVDA tekan H</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
+          <t>Urutan judul tidak melompat-lompat</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>NVDA: tekan H berulang, tulis urutan judul yang terdengar</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Logo utama terbaca oleh screen reader</t>
+          <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, baca semua nama tautan tanpa melihat layar</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Semua tombol dan isian punya nama yang terbaca</t>
+          <t>Logo utama terbaca oleh screen reader</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, dengarkan tautan pertama</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Semua isian formulir punya label yang terhubung</t>
+          <t>Semua tombol dan isian punya nama yang terbaca</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>DevTools tab Accessibility: klik Inspect, baca Computed Properties (Name, Role)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pesan kesalahan formulir dibacakan screen reader</t>
+          <t>Semua isian formulir punya label yang terhubung</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan isian, pilih Inspect, cari &lt;label for=...&gt;</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Warna teks utama cukup kontras dengan latar</t>
+          <t>Pesan kesalahan formulir dibacakan screen reader</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>NVDA + Speech Viewer (NVDA+F5) untuk merekam apa yang diucapkan</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
+          <t>Warna teks utama cukup kontras dengan latar</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan teks, Inspect &gt; eyedropper. Catat 2 kode warna.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
+          <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Browser: tekan Ctrl lalu + dua kali</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Gambar punya keterangan yang benar</t>
+          <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>DevTools: tekan Ctrl+Shift+M, set lebar 320 piksel</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
+          <t>Gambar punya keterangan yang benar</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>DevTools Inspect + NVDA tekan G untuk pindah ke gambar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>File PDF punya judul dan bahasa yang terisi</t>
+          <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Pemutar YouTube: klik tombol CC, putar di detik 0, tengah, dan hampir akhir</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
+          <t>File PDF punya judul dan bahasa yang terisi</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat Reader: Tools &gt; Accessibility &gt; Check PDF Accessibility</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
+          <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Pemutar video + Windows: Settings &gt; Accessibility &gt; Visual effects &gt; Animation effects OFF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan html, Inspect, lihat atribut lang</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Ada cara melapor masalah aksesibilitas</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Cek kaki halaman. NVDA untuk memastikan tautannya terbaca.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1156,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>beranda (Indonesia)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -1038,7 +1166,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>https://www.inovasi.or.id/en/</t>
+          <t>https://www.inovasi.or.id/</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1059,7 +1187,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>nurturing-the-first-steps-of-readi</t>
+          <t>beranda (Inggris)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1069,7 +1197,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>https://www.inovasi.or.id/en/publication/nurturing-the-first-steps-of-reading-in-cirebon</t>
+          <t>https://www.inovasi.or.id/en/</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -2665,12 +2793,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -2684,6 +2812,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2699,46 +2828,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="E2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="F2" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="G2" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="H2" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="I2" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="J2" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="K2" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="L2" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="M2" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="N2" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="O2" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="P2" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="Q2" s="10" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2753,46 +2887,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="P3" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2805,7 +2944,11 @@
           <t>Semua tombol bisa dipakai pakai keyboard saja</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja (Tab, Shift+Tab, Enter, Spasi, Esc, tombol panah). Tetikus tidak dipakai.</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -2819,6 +2962,7 @@
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -2829,7 +2973,11 @@
           <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja + perekam layar (Windows: Win+Alt+R)</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
@@ -2843,6 +2991,7 @@
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -2853,7 +3002,11 @@
           <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard + DevTools: klik kanan elemen, pilih Inspect</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
@@ -2867,6 +3020,7 @@
       <c r="N6" s="9" t="n"/>
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -2877,7 +3031,11 @@
           <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Perekam layar + DevTools tab Accessibility</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -2891,6 +3049,7 @@
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -2901,7 +3060,11 @@
           <t>Ada tombol lompat langsung ke konten utama</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja. Tekan Tab sekali di awal halaman.</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
@@ -2915,6 +3078,7 @@
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -2925,7 +3089,11 @@
           <t>Hanya ada satu bagian header di halaman</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan NVDA+Insert+F7, pilih bagian Landmarks, hitung jumper banner</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
@@ -2939,6 +3107,7 @@
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -2949,7 +3118,11 @@
           <t>Ada tepat satu judul utama (h1)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: ketik document.querySelectorAll('h1').length di Console, atau NVDA tekan H</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
@@ -2963,6 +3136,7 @@
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -2973,7 +3147,11 @@
           <t>Urutan judul tidak melompat-lompat</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan H berulang, tulis urutan judul yang terdengar</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
@@ -2987,6 +3165,7 @@
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -2997,7 +3176,11 @@
           <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, baca semua nama tautan tanpa melihat layar</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -3011,6 +3194,7 @@
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -3021,7 +3205,11 @@
           <t>Logo utama terbaca oleh screen reader</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, dengarkan tautan pertama</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -3035,6 +3223,7 @@
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -3045,7 +3234,11 @@
           <t>Semua tombol dan isian punya nama yang terbaca</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>DevTools tab Accessibility: klik Inspect, baca Computed Properties (Name, Role)</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
@@ -3059,6 +3252,7 @@
       <c r="N14" s="9" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -3069,7 +3263,11 @@
           <t>Semua isian formulir punya label yang terhubung</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan isian, pilih Inspect, cari &lt;label for=...&gt;</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -3083,6 +3281,7 @@
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -3093,7 +3292,11 @@
           <t>Pesan kesalahan formulir dibacakan screen reader</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NVDA + Speech Viewer (NVDA+F5) untuk merekam apa yang diucapkan</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
@@ -3107,6 +3310,7 @@
       <c r="N16" s="9" t="n"/>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -3117,7 +3321,11 @@
           <t>Warna teks utama cukup kontras dengan latar</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan teks, Inspect &gt; eyedropper. Catat 2 kode warna.</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
@@ -3131,6 +3339,7 @@
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -3141,7 +3350,11 @@
           <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Browser: tekan Ctrl lalu + dua kali</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
@@ -3155,6 +3368,7 @@
       <c r="N18" s="9" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -3165,7 +3379,11 @@
           <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: tekan Ctrl+Shift+M, set lebar 320 piksel</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
@@ -3179,6 +3397,7 @@
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -3189,7 +3408,11 @@
           <t>Gambar punya keterangan yang benar</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>DevTools Inspect + NVDA tekan G untuk pindah ke gambar</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
@@ -3203,6 +3426,7 @@
       <c r="N20" s="9" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -3213,7 +3437,11 @@
           <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar YouTube: klik tombol CC, putar di detik 0, tengah, dan hampir akhir</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
@@ -3227,6 +3455,7 @@
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -3237,7 +3466,11 @@
           <t>File PDF punya judul dan bahasa yang terisi</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat Reader: Tools &gt; Accessibility &gt; Check PDF Accessibility</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
@@ -3251,6 +3484,7 @@
       <c r="N22" s="9" t="n"/>
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -3261,7 +3495,11 @@
           <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar video + Windows: Settings &gt; Accessibility &gt; Visual effects &gt; Animation effects OFF</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -3275,6 +3513,7 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -3285,7 +3524,11 @@
           <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan html, Inspect, lihat atribut lang</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -3299,6 +3542,7 @@
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -3309,7 +3553,11 @@
           <t>Ada cara melapor masalah aksesibilitas</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Cek kaki halaman. NVDA untuk memastikan tautannya terbaca.</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
@@ -3323,6 +3571,7 @@
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
@@ -3330,10 +3579,6 @@
           <t>Jumlah gagal</t>
         </is>
       </c>
-      <c r="C27" s="11">
-        <f>COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D27" s="11">
         <f>COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -3386,6 +3631,10 @@
         <f>COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q27" s="11">
+        <f>COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
@@ -3393,10 +3642,6 @@
           <t>Jumlah sudah diuji</t>
         </is>
       </c>
-      <c r="C28" s="12">
-        <f>COUNTIF(C4:C25,"L")+COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D28" s="12">
         <f>COUNTIF(D4:D25,"L")+COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -3449,12 +3694,16 @@
         <f>COUNTIF(P4:P25,"L")+COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q28" s="12">
+        <f>COUNTIF(Q4:Q25,"L")+COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C25">
+  <conditionalFormatting sqref="D4:D25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3462,7 +3711,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D25">
+  <conditionalFormatting sqref="E4:E25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3470,7 +3719,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
+  <conditionalFormatting sqref="F4:F25">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3478,7 +3727,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F25">
+  <conditionalFormatting sqref="G4:G25">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3486,7 +3735,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G25">
+  <conditionalFormatting sqref="H4:H25">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3494,7 +3743,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H25">
+  <conditionalFormatting sqref="I4:I25">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3502,7 +3751,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I25">
+  <conditionalFormatting sqref="J4:J25">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3510,7 +3759,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J25">
+  <conditionalFormatting sqref="K4:K25">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3518,7 +3767,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K25">
+  <conditionalFormatting sqref="L4:L25">
     <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3526,7 +3775,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L25">
+  <conditionalFormatting sqref="M4:M25">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3534,7 +3783,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M25">
+  <conditionalFormatting sqref="N4:N25">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3542,7 +3791,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N25">
+  <conditionalFormatting sqref="O4:O25">
     <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3550,7 +3799,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O25">
+  <conditionalFormatting sqref="P4:P25">
     <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3558,7 +3807,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P25">
+  <conditionalFormatting sqref="Q4:Q25">
     <cfRule type="cellIs" priority="27" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -3567,9 +3816,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="14">
-    <dataValidation sqref="C4:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"L,G,T"</formula1>
-    </dataValidation>
     <dataValidation sqref="D4:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
@@ -3609,6 +3855,9 @@
     <dataValidation sqref="P4:P25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
+    <dataValidation sqref="Q4:Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"L,G,T"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3620,12 +3869,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -3639,6 +3888,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3654,46 +3904,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="E2" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="F2" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="G2" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="H2" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="I2" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="J2" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="K2" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="L2" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="M2" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="N2" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="O2" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="P2" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="Q2" s="10" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3708,46 +3963,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="P3" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="7" t="n">
         <v>28</v>
       </c>
     </row>
@@ -3760,7 +4020,11 @@
           <t>Semua tombol bisa dipakai pakai keyboard saja</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja (Tab, Shift+Tab, Enter, Spasi, Esc, tombol panah). Tetikus tidak dipakai.</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -3774,6 +4038,7 @@
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -3784,7 +4049,11 @@
           <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja + perekam layar (Windows: Win+Alt+R)</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
@@ -3798,6 +4067,7 @@
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -3808,7 +4078,11 @@
           <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard + DevTools: klik kanan elemen, pilih Inspect</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
@@ -3822,6 +4096,7 @@
       <c r="N6" s="9" t="n"/>
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -3832,7 +4107,11 @@
           <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Perekam layar + DevTools tab Accessibility</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -3846,6 +4125,7 @@
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -3856,7 +4136,11 @@
           <t>Ada tombol lompat langsung ke konten utama</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja. Tekan Tab sekali di awal halaman.</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
@@ -3870,6 +4154,7 @@
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -3880,7 +4165,11 @@
           <t>Hanya ada satu bagian header di halaman</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan NVDA+Insert+F7, pilih bagian Landmarks, hitung jumper banner</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
@@ -3894,6 +4183,7 @@
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -3904,7 +4194,11 @@
           <t>Ada tepat satu judul utama (h1)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: ketik document.querySelectorAll('h1').length di Console, atau NVDA tekan H</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
@@ -3918,6 +4212,7 @@
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -3928,7 +4223,11 @@
           <t>Urutan judul tidak melompat-lompat</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan H berulang, tulis urutan judul yang terdengar</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
@@ -3942,6 +4241,7 @@
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -3952,7 +4252,11 @@
           <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, baca semua nama tautan tanpa melihat layar</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -3966,6 +4270,7 @@
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -3976,7 +4281,11 @@
           <t>Logo utama terbaca oleh screen reader</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, dengarkan tautan pertama</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -3990,6 +4299,7 @@
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -4000,7 +4310,11 @@
           <t>Semua tombol dan isian punya nama yang terbaca</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>DevTools tab Accessibility: klik Inspect, baca Computed Properties (Name, Role)</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
@@ -4014,6 +4328,7 @@
       <c r="N14" s="9" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -4024,7 +4339,11 @@
           <t>Semua isian formulir punya label yang terhubung</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan isian, pilih Inspect, cari &lt;label for=...&gt;</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -4038,6 +4357,7 @@
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -4048,7 +4368,11 @@
           <t>Pesan kesalahan formulir dibacakan screen reader</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NVDA + Speech Viewer (NVDA+F5) untuk merekam apa yang diucapkan</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
@@ -4062,6 +4386,7 @@
       <c r="N16" s="9" t="n"/>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -4072,7 +4397,11 @@
           <t>Warna teks utama cukup kontras dengan latar</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan teks, Inspect &gt; eyedropper. Catat 2 kode warna.</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
@@ -4086,6 +4415,7 @@
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -4096,7 +4426,11 @@
           <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Browser: tekan Ctrl lalu + dua kali</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
@@ -4110,6 +4444,7 @@
       <c r="N18" s="9" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -4120,7 +4455,11 @@
           <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: tekan Ctrl+Shift+M, set lebar 320 piksel</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
@@ -4134,6 +4473,7 @@
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -4144,7 +4484,11 @@
           <t>Gambar punya keterangan yang benar</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>DevTools Inspect + NVDA tekan G untuk pindah ke gambar</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
@@ -4158,6 +4502,7 @@
       <c r="N20" s="9" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -4168,7 +4513,11 @@
           <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar YouTube: klik tombol CC, putar di detik 0, tengah, dan hampir akhir</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
@@ -4182,6 +4531,7 @@
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -4192,7 +4542,11 @@
           <t>File PDF punya judul dan bahasa yang terisi</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat Reader: Tools &gt; Accessibility &gt; Check PDF Accessibility</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
@@ -4206,6 +4560,7 @@
       <c r="N22" s="9" t="n"/>
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -4216,7 +4571,11 @@
           <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar video + Windows: Settings &gt; Accessibility &gt; Visual effects &gt; Animation effects OFF</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -4230,6 +4589,7 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -4240,7 +4600,11 @@
           <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan html, Inspect, lihat atribut lang</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -4254,6 +4618,7 @@
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -4264,7 +4629,11 @@
           <t>Ada cara melapor masalah aksesibilitas</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Cek kaki halaman. NVDA untuk memastikan tautannya terbaca.</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
@@ -4278,6 +4647,7 @@
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
@@ -4285,10 +4655,6 @@
           <t>Jumlah gagal</t>
         </is>
       </c>
-      <c r="C27" s="11">
-        <f>COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D27" s="11">
         <f>COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -4341,6 +4707,10 @@
         <f>COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q27" s="11">
+        <f>COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
@@ -4348,10 +4718,6 @@
           <t>Jumlah sudah diuji</t>
         </is>
       </c>
-      <c r="C28" s="12">
-        <f>COUNTIF(C4:C25,"L")+COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D28" s="12">
         <f>COUNTIF(D4:D25,"L")+COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -4404,12 +4770,16 @@
         <f>COUNTIF(P4:P25,"L")+COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q28" s="12">
+        <f>COUNTIF(Q4:Q25,"L")+COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C25">
+  <conditionalFormatting sqref="D4:D25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4417,7 +4787,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D25">
+  <conditionalFormatting sqref="E4:E25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4425,7 +4795,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
+  <conditionalFormatting sqref="F4:F25">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4433,7 +4803,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F25">
+  <conditionalFormatting sqref="G4:G25">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4441,7 +4811,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G25">
+  <conditionalFormatting sqref="H4:H25">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4449,7 +4819,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H25">
+  <conditionalFormatting sqref="I4:I25">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4457,7 +4827,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I25">
+  <conditionalFormatting sqref="J4:J25">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4465,7 +4835,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J25">
+  <conditionalFormatting sqref="K4:K25">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4473,7 +4843,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K25">
+  <conditionalFormatting sqref="L4:L25">
     <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4481,7 +4851,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L25">
+  <conditionalFormatting sqref="M4:M25">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4489,7 +4859,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M25">
+  <conditionalFormatting sqref="N4:N25">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4497,7 +4867,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N25">
+  <conditionalFormatting sqref="O4:O25">
     <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4505,7 +4875,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O25">
+  <conditionalFormatting sqref="P4:P25">
     <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4513,7 +4883,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P25">
+  <conditionalFormatting sqref="Q4:Q25">
     <cfRule type="cellIs" priority="27" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -4522,9 +4892,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="14">
-    <dataValidation sqref="C4:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"L,G,T"</formula1>
-    </dataValidation>
     <dataValidation sqref="D4:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
@@ -4564,6 +4931,9 @@
     <dataValidation sqref="P4:P25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
+    <dataValidation sqref="Q4:Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"L,G,T"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4575,12 +4945,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -4594,6 +4964,7 @@
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4609,46 +4980,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="E2" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="F2" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="G2" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="H2" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="I2" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="J2" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="K2" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="L2" s="10" t="n">
         <v>37</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="M2" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="N2" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="O2" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="O2" s="10" t="n">
+      <c r="P2" s="10" t="n">
         <v>41</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="Q2" s="10" t="n">
         <v>42</v>
       </c>
     </row>
@@ -4663,46 +5039,51 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="O3" s="7" t="n">
+      <c r="P3" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="P3" s="7" t="n">
+      <c r="Q3" s="7" t="n">
         <v>42</v>
       </c>
     </row>
@@ -4715,7 +5096,11 @@
           <t>Semua tombol bisa dipakai pakai keyboard saja</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja (Tab, Shift+Tab, Enter, Spasi, Esc, tombol panah). Tetikus tidak dipakai.</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -4729,6 +5114,7 @@
       <c r="N4" s="9" t="n"/>
       <c r="O4" s="9" t="n"/>
       <c r="P4" s="9" t="n"/>
+      <c r="Q4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -4739,7 +5125,11 @@
           <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja + perekam layar (Windows: Win+Alt+R)</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
@@ -4753,6 +5143,7 @@
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
       <c r="P5" s="9" t="n"/>
+      <c r="Q5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -4763,7 +5154,11 @@
           <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard + DevTools: klik kanan elemen, pilih Inspect</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
@@ -4777,6 +5172,7 @@
       <c r="N6" s="9" t="n"/>
       <c r="O6" s="9" t="n"/>
       <c r="P6" s="9" t="n"/>
+      <c r="Q6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -4787,7 +5183,11 @@
           <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Perekam layar + DevTools tab Accessibility</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -4801,6 +5201,7 @@
       <c r="N7" s="9" t="n"/>
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="9" t="n"/>
+      <c r="Q7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -4811,7 +5212,11 @@
           <t>Ada tombol lompat langsung ke konten utama</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja. Tekan Tab sekali di awal halaman.</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
@@ -4825,6 +5230,7 @@
       <c r="N8" s="9" t="n"/>
       <c r="O8" s="9" t="n"/>
       <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -4835,7 +5241,11 @@
           <t>Hanya ada satu bagian header di halaman</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan NVDA+Insert+F7, pilih bagian Landmarks, hitung jumper banner</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
@@ -4849,6 +5259,7 @@
       <c r="N9" s="9" t="n"/>
       <c r="O9" s="9" t="n"/>
       <c r="P9" s="9" t="n"/>
+      <c r="Q9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -4859,7 +5270,11 @@
           <t>Ada tepat satu judul utama (h1)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: ketik document.querySelectorAll('h1').length di Console, atau NVDA tekan H</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
@@ -4873,6 +5288,7 @@
       <c r="N10" s="9" t="n"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="9" t="n"/>
+      <c r="Q10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -4883,7 +5299,11 @@
           <t>Urutan judul tidak melompat-lompat</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan H berulang, tulis urutan judul yang terdengar</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
@@ -4897,6 +5317,7 @@
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="9" t="n"/>
+      <c r="Q11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -4907,7 +5328,11 @@
           <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, baca semua nama tautan tanpa melihat layar</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -4921,6 +5346,7 @@
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
       <c r="P12" s="9" t="n"/>
+      <c r="Q12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -4931,7 +5357,11 @@
           <t>Logo utama terbaca oleh screen reader</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, dengarkan tautan pertama</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -4945,6 +5375,7 @@
       <c r="N13" s="9" t="n"/>
       <c r="O13" s="9" t="n"/>
       <c r="P13" s="9" t="n"/>
+      <c r="Q13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -4955,7 +5386,11 @@
           <t>Semua tombol dan isian punya nama yang terbaca</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>DevTools tab Accessibility: klik Inspect, baca Computed Properties (Name, Role)</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
@@ -4969,6 +5404,7 @@
       <c r="N14" s="9" t="n"/>
       <c r="O14" s="9" t="n"/>
       <c r="P14" s="9" t="n"/>
+      <c r="Q14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -4979,7 +5415,11 @@
           <t>Semua isian formulir punya label yang terhubung</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan isian, pilih Inspect, cari &lt;label for=...&gt;</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -4993,6 +5433,7 @@
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
+      <c r="Q15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -5003,7 +5444,11 @@
           <t>Pesan kesalahan formulir dibacakan screen reader</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NVDA + Speech Viewer (NVDA+F5) untuk merekam apa yang diucapkan</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
@@ -5017,6 +5462,7 @@
       <c r="N16" s="9" t="n"/>
       <c r="O16" s="9" t="n"/>
       <c r="P16" s="9" t="n"/>
+      <c r="Q16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -5027,7 +5473,11 @@
           <t>Warna teks utama cukup kontras dengan latar</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan teks, Inspect &gt; eyedropper. Catat 2 kode warna.</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
@@ -5041,6 +5491,7 @@
       <c r="N17" s="9" t="n"/>
       <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
+      <c r="Q17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -5051,7 +5502,11 @@
           <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Browser: tekan Ctrl lalu + dua kali</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
@@ -5065,6 +5520,7 @@
       <c r="N18" s="9" t="n"/>
       <c r="O18" s="9" t="n"/>
       <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -5075,7 +5531,11 @@
           <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: tekan Ctrl+Shift+M, set lebar 320 piksel</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
@@ -5089,6 +5549,7 @@
       <c r="N19" s="9" t="n"/>
       <c r="O19" s="9" t="n"/>
       <c r="P19" s="9" t="n"/>
+      <c r="Q19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -5099,7 +5560,11 @@
           <t>Gambar punya keterangan yang benar</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>DevTools Inspect + NVDA tekan G untuk pindah ke gambar</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
@@ -5113,6 +5578,7 @@
       <c r="N20" s="9" t="n"/>
       <c r="O20" s="9" t="n"/>
       <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -5123,7 +5589,11 @@
           <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar YouTube: klik tombol CC, putar di detik 0, tengah, dan hampir akhir</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
@@ -5137,6 +5607,7 @@
       <c r="N21" s="9" t="n"/>
       <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
+      <c r="Q21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -5147,7 +5618,11 @@
           <t>File PDF punya judul dan bahasa yang terisi</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat Reader: Tools &gt; Accessibility &gt; Check PDF Accessibility</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
@@ -5161,6 +5636,7 @@
       <c r="N22" s="9" t="n"/>
       <c r="O22" s="9" t="n"/>
       <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -5171,7 +5647,11 @@
           <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar video + Windows: Settings &gt; Accessibility &gt; Visual effects &gt; Animation effects OFF</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -5185,6 +5665,7 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -5195,7 +5676,11 @@
           <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan html, Inspect, lihat atribut lang</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -5209,6 +5694,7 @@
       <c r="N24" s="9" t="n"/>
       <c r="O24" s="9" t="n"/>
       <c r="P24" s="9" t="n"/>
+      <c r="Q24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -5219,7 +5705,11 @@
           <t>Ada cara melapor masalah aksesibilitas</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Cek kaki halaman. NVDA untuk memastikan tautannya terbaca.</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
@@ -5233,6 +5723,7 @@
       <c r="N25" s="9" t="n"/>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
+      <c r="Q25" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
@@ -5240,10 +5731,6 @@
           <t>Jumlah gagal</t>
         </is>
       </c>
-      <c r="C27" s="11">
-        <f>COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D27" s="11">
         <f>COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -5296,6 +5783,10 @@
         <f>COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q27" s="11">
+        <f>COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
@@ -5303,10 +5794,6 @@
           <t>Jumlah sudah diuji</t>
         </is>
       </c>
-      <c r="C28" s="12">
-        <f>COUNTIF(C4:C25,"L")+COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D28" s="12">
         <f>COUNTIF(D4:D25,"L")+COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -5359,12 +5846,16 @@
         <f>COUNTIF(P4:P25,"L")+COUNTIF(P4:P25,"G")</f>
         <v/>
       </c>
+      <c r="Q28" s="12">
+        <f>COUNTIF(Q4:Q25,"L")+COUNTIF(Q4:Q25,"G")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C25">
+  <conditionalFormatting sqref="D4:D25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5372,7 +5863,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D25">
+  <conditionalFormatting sqref="E4:E25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5380,7 +5871,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
+  <conditionalFormatting sqref="F4:F25">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5388,7 +5879,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F25">
+  <conditionalFormatting sqref="G4:G25">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5396,7 +5887,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G25">
+  <conditionalFormatting sqref="H4:H25">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5404,7 +5895,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H25">
+  <conditionalFormatting sqref="I4:I25">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5412,7 +5903,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I25">
+  <conditionalFormatting sqref="J4:J25">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5420,7 +5911,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J25">
+  <conditionalFormatting sqref="K4:K25">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5428,7 +5919,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K25">
+  <conditionalFormatting sqref="L4:L25">
     <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5436,7 +5927,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L25">
+  <conditionalFormatting sqref="M4:M25">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5444,7 +5935,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M25">
+  <conditionalFormatting sqref="N4:N25">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5452,7 +5943,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N25">
+  <conditionalFormatting sqref="O4:O25">
     <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5460,7 +5951,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4:O25">
+  <conditionalFormatting sqref="P4:P25">
     <cfRule type="cellIs" priority="25" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5468,7 +5959,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P4:P25">
+  <conditionalFormatting sqref="Q4:Q25">
     <cfRule type="cellIs" priority="27" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -5477,9 +5968,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="14">
-    <dataValidation sqref="C4:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"L,G,T"</formula1>
-    </dataValidation>
     <dataValidation sqref="D4:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
@@ -5519,6 +6007,9 @@
     <dataValidation sqref="P4:P25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
+    <dataValidation sqref="Q4:Q25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"L,G,T"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5530,12 +6021,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -5547,6 +6038,7 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -5562,40 +6054,45 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="n">
         <v>43</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="E2" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="F2" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="G2" s="10" t="n">
         <v>46</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="H2" s="10" t="n">
         <v>47</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="I2" s="10" t="n">
         <v>48</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="J2" s="10" t="n">
         <v>49</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="K2" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="L2" s="10" t="n">
         <v>51</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="M2" s="10" t="n">
         <v>52</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="N2" s="10" t="n">
         <v>53</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="O2" s="10" t="n">
         <v>54</v>
       </c>
     </row>
@@ -5610,40 +6107,45 @@
           <t>Yang diperiksa</t>
         </is>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Alat yang dipakai</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="D3" s="7" t="n">
+      <c r="E3" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="F3" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="G3" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="H3" s="7" t="n">
+      <c r="I3" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="I3" s="7" t="n">
+      <c r="J3" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="J3" s="7" t="n">
+      <c r="K3" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="K3" s="7" t="n">
+      <c r="L3" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="L3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="O3" s="7" t="n">
         <v>54</v>
       </c>
     </row>
@@ -5656,7 +6158,11 @@
           <t>Semua tombol bisa dipakai pakai keyboard saja</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n"/>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja (Tab, Shift+Tab, Enter, Spasi, Esc, tombol panah). Tetikus tidak dipakai.</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
       <c r="F4" s="9" t="n"/>
@@ -5668,6 +6174,7 @@
       <c r="L4" s="9" t="n"/>
       <c r="M4" s="9" t="n"/>
       <c r="N4" s="9" t="n"/>
+      <c r="O4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="n">
@@ -5678,7 +6185,11 @@
           <t>Tidak terjebak di dalam galeri, menu, atau searching</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja + perekam layar (Windows: Win+Alt+R)</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
@@ -5690,6 +6201,7 @@
       <c r="L5" s="9" t="n"/>
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="n">
@@ -5700,7 +6212,11 @@
           <t>Urutan fokus masuk akal, mengikuti urutan yang dilihat mata</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard + DevTools: klik kanan elemen, pilih Inspect</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="n"/>
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="9" t="n"/>
@@ -5712,6 +6228,7 @@
       <c r="L6" s="9" t="n"/>
       <c r="M6" s="9" t="n"/>
       <c r="N6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="n">
@@ -5722,7 +6239,11 @@
           <t>Kotak fokus terlihat jelas saat memakai keyboard</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Perekam layar + DevTools tab Accessibility</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
@@ -5734,6 +6255,7 @@
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="n">
@@ -5744,7 +6266,11 @@
           <t>Ada tombol lompat langsung ke konten utama</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Keyboard saja. Tekan Tab sekali di awal halaman.</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="9" t="n"/>
@@ -5756,6 +6282,7 @@
       <c r="L8" s="9" t="n"/>
       <c r="M8" s="9" t="n"/>
       <c r="N8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n">
@@ -5766,7 +6293,11 @@
           <t>Hanya ada satu bagian header di halaman</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan NVDA+Insert+F7, pilih bagian Landmarks, hitung jumper banner</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
@@ -5778,6 +6309,7 @@
       <c r="L9" s="9" t="n"/>
       <c r="M9" s="9" t="n"/>
       <c r="N9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="n">
@@ -5788,7 +6320,11 @@
           <t>Ada tepat satu judul utama (h1)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: ketik document.querySelectorAll('h1').length di Console, atau NVDA tekan H</t>
+        </is>
+      </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="9" t="n"/>
@@ -5800,6 +6336,7 @@
       <c r="L10" s="9" t="n"/>
       <c r="M10" s="9" t="n"/>
       <c r="N10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="n">
@@ -5810,7 +6347,11 @@
           <t>Urutan judul tidak melompat-lompat</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan H berulang, tulis urutan judul yang terdengar</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
@@ -5822,6 +6363,7 @@
       <c r="L11" s="9" t="n"/>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="n">
@@ -5832,7 +6374,11 @@
           <t>Semua tautan punya tulisan yang menjelaskan tujuan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, baca semua nama tautan tanpa melihat layar</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
@@ -5844,6 +6390,7 @@
       <c r="L12" s="9" t="n"/>
       <c r="M12" s="9" t="n"/>
       <c r="N12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n">
@@ -5854,7 +6401,11 @@
           <t>Logo utama terbaca oleh screen reader</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NVDA: tekan K, dengarkan tautan pertama</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
@@ -5866,6 +6417,7 @@
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
       <c r="N13" s="9" t="n"/>
+      <c r="O13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="9" t="n">
@@ -5876,7 +6428,11 @@
           <t>Semua tombol dan isian punya nama yang terbaca</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>DevTools tab Accessibility: klik Inspect, baca Computed Properties (Name, Role)</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
@@ -5888,6 +6444,7 @@
       <c r="L14" s="9" t="n"/>
       <c r="M14" s="9" t="n"/>
       <c r="N14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -5898,7 +6455,11 @@
           <t>Semua isian formulir punya label yang terhubung</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan isian, pilih Inspect, cari &lt;label for=...&gt;</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -5910,6 +6471,7 @@
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="9" t="n">
@@ -5920,7 +6482,11 @@
           <t>Pesan kesalahan formulir dibacakan screen reader</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>NVDA + Speech Viewer (NVDA+F5) untuk merekam apa yang diucapkan</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
       <c r="F16" s="9" t="n"/>
@@ -5932,6 +6498,7 @@
       <c r="L16" s="9" t="n"/>
       <c r="M16" s="9" t="n"/>
       <c r="N16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -5942,7 +6509,11 @@
           <t>Warna teks utama cukup kontras dengan latar</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan teks, Inspect &gt; eyedropper. Catat 2 kode warna.</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
@@ -5954,6 +6525,7 @@
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="9" t="n">
@@ -5964,7 +6536,11 @@
           <t>Teks masih terbaca saat halaman dizoom 200 persen</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Browser: tekan Ctrl lalu + dua kali</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
       <c r="F18" s="9" t="n"/>
@@ -5976,6 +6552,7 @@
       <c r="L18" s="9" t="n"/>
       <c r="M18" s="9" t="n"/>
       <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n">
@@ -5986,7 +6563,11 @@
           <t>Tidak ada gulir ke samping saat layar 320 piksel</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: tekan Ctrl+Shift+M, set lebar 320 piksel</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
@@ -5998,6 +6579,7 @@
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
       <c r="N19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="9" t="n">
@@ -6008,7 +6590,11 @@
           <t>Gambar punya keterangan yang benar</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>DevTools Inspect + NVDA tekan G untuk pindah ke gambar</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
       <c r="F20" s="9" t="n"/>
@@ -6020,6 +6606,7 @@
       <c r="L20" s="9" t="n"/>
       <c r="M20" s="9" t="n"/>
       <c r="N20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n">
@@ -6030,7 +6617,11 @@
           <t>Video punya subtitle Bahasa Indonesia yang cocok dengan suara</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar YouTube: klik tombol CC, putar di detik 0, tengah, dan hampir akhir</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
@@ -6042,6 +6633,7 @@
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="9" t="n">
@@ -6052,7 +6644,11 @@
           <t>File PDF punya judul dan bahasa yang terisi</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Adobe Acrobat Reader: Tools &gt; Accessibility &gt; Check PDF Accessibility</t>
+        </is>
+      </c>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
       <c r="F22" s="9" t="n"/>
@@ -6064,6 +6660,7 @@
       <c r="L22" s="9" t="n"/>
       <c r="M22" s="9" t="n"/>
       <c r="N22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="9" t="n">
@@ -6074,7 +6671,11 @@
           <t>Tidak ada dua gambar atau cahaya yang berkedip cepat</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Pemutar video + Windows: Settings &gt; Accessibility &gt; Visual effects &gt; Animation effects OFF</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -6086,6 +6687,7 @@
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n">
@@ -6096,7 +6698,11 @@
           <t>Bahasa halaman ditandai dengan benar (id-ID)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>DevTools: klik kanan html, Inspect, lihat atribut lang</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
       <c r="F24" s="9" t="n"/>
@@ -6108,6 +6714,7 @@
       <c r="L24" s="9" t="n"/>
       <c r="M24" s="9" t="n"/>
       <c r="N24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -6118,7 +6725,11 @@
           <t>Ada cara melapor masalah aksesibilitas</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Cek kaki halaman. NVDA untuk memastikan tautannya terbaca.</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
@@ -6130,6 +6741,7 @@
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
       <c r="N25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
@@ -6137,10 +6749,6 @@
           <t>Jumlah gagal</t>
         </is>
       </c>
-      <c r="C27" s="11">
-        <f>COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D27" s="11">
         <f>COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -6185,6 +6793,10 @@
         <f>COUNTIF(N4:N25,"G")</f>
         <v/>
       </c>
+      <c r="O27" s="11">
+        <f>COUNTIF(O4:O25,"G")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
@@ -6192,10 +6804,6 @@
           <t>Jumlah sudah diuji</t>
         </is>
       </c>
-      <c r="C28" s="12">
-        <f>COUNTIF(C4:C25,"L")+COUNTIF(C4:C25,"G")</f>
-        <v/>
-      </c>
       <c r="D28" s="12">
         <f>COUNTIF(D4:D25,"L")+COUNTIF(D4:D25,"G")</f>
         <v/>
@@ -6240,12 +6848,16 @@
         <f>COUNTIF(N4:N25,"L")+COUNTIF(N4:N25,"G")</f>
         <v/>
       </c>
+      <c r="O28" s="12">
+        <f>COUNTIF(O4:O25,"L")+COUNTIF(O4:O25,"G")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:C25">
+  <conditionalFormatting sqref="D4:D25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6253,7 +6865,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D25">
+  <conditionalFormatting sqref="E4:E25">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6261,7 +6873,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E25">
+  <conditionalFormatting sqref="F4:F25">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6269,7 +6881,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F25">
+  <conditionalFormatting sqref="G4:G25">
     <cfRule type="cellIs" priority="7" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6277,7 +6889,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G25">
+  <conditionalFormatting sqref="H4:H25">
     <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6285,7 +6897,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H25">
+  <conditionalFormatting sqref="I4:I25">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6293,7 +6905,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:I25">
+  <conditionalFormatting sqref="J4:J25">
     <cfRule type="cellIs" priority="13" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6301,7 +6913,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J25">
+  <conditionalFormatting sqref="K4:K25">
     <cfRule type="cellIs" priority="15" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6309,7 +6921,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K4:K25">
+  <conditionalFormatting sqref="L4:L25">
     <cfRule type="cellIs" priority="17" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6317,7 +6929,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L4:L25">
+  <conditionalFormatting sqref="M4:M25">
     <cfRule type="cellIs" priority="19" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6325,7 +6937,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M4:M25">
+  <conditionalFormatting sqref="N4:N25">
     <cfRule type="cellIs" priority="21" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6333,7 +6945,7 @@
       <formula>"L"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:N25">
+  <conditionalFormatting sqref="O4:O25">
     <cfRule type="cellIs" priority="23" operator="equal" dxfId="0">
       <formula>"G"</formula>
     </cfRule>
@@ -6342,9 +6954,6 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="12">
-    <dataValidation sqref="C4:C25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"L,G,T"</formula1>
-    </dataValidation>
     <dataValidation sqref="D4:D25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
@@ -6376,6 +6985,9 @@
       <formula1>"L,G,T"</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"L,G,T"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O4:O25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"L,G,T"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7787,7 +8399,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>beranda (Indonesia)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
@@ -7796,11 +8408,11 @@
         </is>
       </c>
       <c r="D4" s="13">
-        <f>'25'!C26</f>
+        <f>'02-Uji-Halaman-01-14'!D26</f>
         <v/>
       </c>
       <c r="E4" s="13">
-        <f>'25'!C27</f>
+        <f>'02-Uji-Halaman-01-14'!D27</f>
         <v/>
       </c>
       <c r="F4" s="9" t="n"/>
@@ -7814,7 +8426,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>nurturing-the-first-steps-of-readi</t>
+          <t>beranda (Inggris)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -7823,11 +8435,11 @@
         </is>
       </c>
       <c r="D5" s="13">
-        <f>'25'!D26</f>
+        <f>'02-Uji-Halaman-01-14'!E26</f>
         <v/>
       </c>
       <c r="E5" s="13">
-        <f>'25'!D27</f>
+        <f>'02-Uji-Halaman-01-14'!E27</f>
         <v/>
       </c>
       <c r="F5" s="9" t="n"/>
@@ -7850,11 +8462,11 @@
         </is>
       </c>
       <c r="D6" s="13">
-        <f>'25'!E26</f>
+        <f>'02-Uji-Halaman-01-14'!F26</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>'25'!E27</f>
+        <f>'02-Uji-Halaman-01-14'!F27</f>
         <v/>
       </c>
       <c r="F6" s="9" t="n"/>
@@ -7877,11 +8489,11 @@
         </is>
       </c>
       <c r="D7" s="13">
-        <f>'25'!F26</f>
+        <f>'02-Uji-Halaman-01-14'!G26</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>'25'!F27</f>
+        <f>'02-Uji-Halaman-01-14'!G27</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n"/>
@@ -7904,11 +8516,11 @@
         </is>
       </c>
       <c r="D8" s="13">
-        <f>'25'!G26</f>
+        <f>'02-Uji-Halaman-01-14'!H26</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>'25'!G27</f>
+        <f>'02-Uji-Halaman-01-14'!H27</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n"/>
@@ -7931,11 +8543,11 @@
         </is>
       </c>
       <c r="D9" s="13">
-        <f>'25'!H26</f>
+        <f>'02-Uji-Halaman-01-14'!I26</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>'25'!H27</f>
+        <f>'02-Uji-Halaman-01-14'!I27</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -7958,11 +8570,11 @@
         </is>
       </c>
       <c r="D10" s="13">
-        <f>'25'!I26</f>
+        <f>'02-Uji-Halaman-01-14'!J26</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>'25'!I27</f>
+        <f>'02-Uji-Halaman-01-14'!J27</f>
         <v/>
       </c>
       <c r="F10" s="9" t="n"/>
@@ -7985,11 +8597,11 @@
         </is>
       </c>
       <c r="D11" s="13">
-        <f>'25'!J26</f>
+        <f>'02-Uji-Halaman-01-14'!K26</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>'25'!J27</f>
+        <f>'02-Uji-Halaman-01-14'!K27</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n"/>
@@ -8012,11 +8624,11 @@
         </is>
       </c>
       <c r="D12" s="13">
-        <f>'25'!K26</f>
+        <f>'02-Uji-Halaman-01-14'!L26</f>
         <v/>
       </c>
       <c r="E12" s="13">
-        <f>'25'!K27</f>
+        <f>'02-Uji-Halaman-01-14'!L27</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n"/>
@@ -8039,11 +8651,11 @@
         </is>
       </c>
       <c r="D13" s="13">
-        <f>'25'!L26</f>
+        <f>'02-Uji-Halaman-01-14'!M26</f>
         <v/>
       </c>
       <c r="E13" s="13">
-        <f>'25'!L27</f>
+        <f>'02-Uji-Halaman-01-14'!M27</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n"/>
@@ -8066,11 +8678,11 @@
         </is>
       </c>
       <c r="D14" s="13">
-        <f>'25'!M26</f>
+        <f>'02-Uji-Halaman-01-14'!N26</f>
         <v/>
       </c>
       <c r="E14" s="13">
-        <f>'25'!M27</f>
+        <f>'02-Uji-Halaman-01-14'!N27</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n"/>
@@ -8093,11 +8705,11 @@
         </is>
       </c>
       <c r="D15" s="13">
-        <f>'25'!N26</f>
+        <f>'02-Uji-Halaman-01-14'!O26</f>
         <v/>
       </c>
       <c r="E15" s="13">
-        <f>'25'!N27</f>
+        <f>'02-Uji-Halaman-01-14'!O27</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n"/>
@@ -8120,11 +8732,11 @@
         </is>
       </c>
       <c r="D16" s="13">
-        <f>'25'!O26</f>
+        <f>'02-Uji-Halaman-01-14'!P26</f>
         <v/>
       </c>
       <c r="E16" s="13">
-        <f>'25'!O27</f>
+        <f>'02-Uji-Halaman-01-14'!P27</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n"/>
@@ -8147,11 +8759,11 @@
         </is>
       </c>
       <c r="D17" s="13">
-        <f>'25'!P26</f>
+        <f>'02-Uji-Halaman-01-14'!Q26</f>
         <v/>
       </c>
       <c r="E17" s="13">
-        <f>'25'!P27</f>
+        <f>'02-Uji-Halaman-01-14'!Q27</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n"/>
@@ -8174,11 +8786,11 @@
         </is>
       </c>
       <c r="D18" s="13">
-        <f>'25'!C26</f>
+        <f>'03-Uji-Halaman-15-28'!D26</f>
         <v/>
       </c>
       <c r="E18" s="13">
-        <f>'25'!C27</f>
+        <f>'03-Uji-Halaman-15-28'!D27</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -8201,11 +8813,11 @@
         </is>
       </c>
       <c r="D19" s="13">
-        <f>'25'!D26</f>
+        <f>'03-Uji-Halaman-15-28'!E26</f>
         <v/>
       </c>
       <c r="E19" s="13">
-        <f>'25'!D27</f>
+        <f>'03-Uji-Halaman-15-28'!E27</f>
         <v/>
       </c>
       <c r="F19" s="9" t="n"/>
@@ -8228,11 +8840,11 @@
         </is>
       </c>
       <c r="D20" s="13">
-        <f>'25'!E26</f>
+        <f>'03-Uji-Halaman-15-28'!F26</f>
         <v/>
       </c>
       <c r="E20" s="13">
-        <f>'25'!E27</f>
+        <f>'03-Uji-Halaman-15-28'!F27</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n"/>
@@ -8255,11 +8867,11 @@
         </is>
       </c>
       <c r="D21" s="13">
-        <f>'25'!F26</f>
+        <f>'03-Uji-Halaman-15-28'!G26</f>
         <v/>
       </c>
       <c r="E21" s="13">
-        <f>'25'!F27</f>
+        <f>'03-Uji-Halaman-15-28'!G27</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n"/>
@@ -8282,11 +8894,11 @@
         </is>
       </c>
       <c r="D22" s="13">
-        <f>'25'!G26</f>
+        <f>'03-Uji-Halaman-15-28'!H26</f>
         <v/>
       </c>
       <c r="E22" s="13">
-        <f>'25'!G27</f>
+        <f>'03-Uji-Halaman-15-28'!H27</f>
         <v/>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -8309,11 +8921,11 @@
         </is>
       </c>
       <c r="D23" s="13">
-        <f>'25'!H26</f>
+        <f>'03-Uji-Halaman-15-28'!I26</f>
         <v/>
       </c>
       <c r="E23" s="13">
-        <f>'25'!H27</f>
+        <f>'03-Uji-Halaman-15-28'!I27</f>
         <v/>
       </c>
       <c r="F23" s="9" t="n"/>
@@ -8336,11 +8948,11 @@
         </is>
       </c>
       <c r="D24" s="13">
-        <f>'25'!I26</f>
+        <f>'03-Uji-Halaman-15-28'!J26</f>
         <v/>
       </c>
       <c r="E24" s="13">
-        <f>'25'!I27</f>
+        <f>'03-Uji-Halaman-15-28'!J27</f>
         <v/>
       </c>
       <c r="F24" s="9" t="n"/>
@@ -8363,11 +8975,11 @@
         </is>
       </c>
       <c r="D25" s="13">
-        <f>'25'!J26</f>
+        <f>'03-Uji-Halaman-15-28'!K26</f>
         <v/>
       </c>
       <c r="E25" s="13">
-        <f>'25'!J27</f>
+        <f>'03-Uji-Halaman-15-28'!K27</f>
         <v/>
       </c>
       <c r="F25" s="9" t="n"/>
@@ -8390,11 +9002,11 @@
         </is>
       </c>
       <c r="D26" s="13">
-        <f>'25'!K26</f>
+        <f>'03-Uji-Halaman-15-28'!L26</f>
         <v/>
       </c>
       <c r="E26" s="13">
-        <f>'25'!K27</f>
+        <f>'03-Uji-Halaman-15-28'!L27</f>
         <v/>
       </c>
       <c r="F26" s="9" t="n"/>
@@ -8417,11 +9029,11 @@
         </is>
       </c>
       <c r="D27" s="13">
-        <f>'25'!L26</f>
+        <f>'03-Uji-Halaman-15-28'!M26</f>
         <v/>
       </c>
       <c r="E27" s="13">
-        <f>'25'!L27</f>
+        <f>'03-Uji-Halaman-15-28'!M27</f>
         <v/>
       </c>
       <c r="F27" s="9" t="n"/>
@@ -8444,11 +9056,11 @@
         </is>
       </c>
       <c r="D28" s="13">
-        <f>'25'!M26</f>
+        <f>'03-Uji-Halaman-15-28'!N26</f>
         <v/>
       </c>
       <c r="E28" s="13">
-        <f>'25'!M27</f>
+        <f>'03-Uji-Halaman-15-28'!N27</f>
         <v/>
       </c>
       <c r="F28" s="9" t="n"/>
@@ -8471,11 +9083,11 @@
         </is>
       </c>
       <c r="D29" s="13">
-        <f>'25'!N26</f>
+        <f>'03-Uji-Halaman-15-28'!O26</f>
         <v/>
       </c>
       <c r="E29" s="13">
-        <f>'25'!N27</f>
+        <f>'03-Uji-Halaman-15-28'!O27</f>
         <v/>
       </c>
       <c r="F29" s="9" t="n"/>
@@ -8498,11 +9110,11 @@
         </is>
       </c>
       <c r="D30" s="13">
-        <f>'25'!O26</f>
+        <f>'03-Uji-Halaman-15-28'!P26</f>
         <v/>
       </c>
       <c r="E30" s="13">
-        <f>'25'!O27</f>
+        <f>'03-Uji-Halaman-15-28'!P27</f>
         <v/>
       </c>
       <c r="F30" s="9" t="n"/>
@@ -8525,11 +9137,11 @@
         </is>
       </c>
       <c r="D31" s="13">
-        <f>'25'!P26</f>
+        <f>'03-Uji-Halaman-15-28'!Q26</f>
         <v/>
       </c>
       <c r="E31" s="13">
-        <f>'25'!P27</f>
+        <f>'03-Uji-Halaman-15-28'!Q27</f>
         <v/>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -8552,11 +9164,11 @@
         </is>
       </c>
       <c r="D32" s="13">
-        <f>'25'!C26</f>
+        <f>'04-Uji-Halaman-29-42'!D26</f>
         <v/>
       </c>
       <c r="E32" s="13">
-        <f>'25'!C27</f>
+        <f>'04-Uji-Halaman-29-42'!D27</f>
         <v/>
       </c>
       <c r="F32" s="9" t="n"/>
@@ -8579,11 +9191,11 @@
         </is>
       </c>
       <c r="D33" s="13">
-        <f>'25'!D26</f>
+        <f>'04-Uji-Halaman-29-42'!E26</f>
         <v/>
       </c>
       <c r="E33" s="13">
-        <f>'25'!D27</f>
+        <f>'04-Uji-Halaman-29-42'!E27</f>
         <v/>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -8606,11 +9218,11 @@
         </is>
       </c>
       <c r="D34" s="13">
-        <f>'25'!E26</f>
+        <f>'04-Uji-Halaman-29-42'!F26</f>
         <v/>
       </c>
       <c r="E34" s="13">
-        <f>'25'!E27</f>
+        <f>'04-Uji-Halaman-29-42'!F27</f>
         <v/>
       </c>
       <c r="F34" s="9" t="n"/>
@@ -8633,11 +9245,11 @@
         </is>
       </c>
       <c r="D35" s="13">
-        <f>'25'!F26</f>
+        <f>'04-Uji-Halaman-29-42'!G26</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>'25'!F27</f>
+        <f>'04-Uji-Halaman-29-42'!G27</f>
         <v/>
       </c>
       <c r="F35" s="9" t="n"/>
@@ -8660,11 +9272,11 @@
         </is>
       </c>
       <c r="D36" s="13">
-        <f>'25'!G26</f>
+        <f>'04-Uji-Halaman-29-42'!H26</f>
         <v/>
       </c>
       <c r="E36" s="13">
-        <f>'25'!G27</f>
+        <f>'04-Uji-Halaman-29-42'!H27</f>
         <v/>
       </c>
       <c r="F36" s="9" t="n"/>
@@ -8687,11 +9299,11 @@
         </is>
       </c>
       <c r="D37" s="13">
-        <f>'25'!H26</f>
+        <f>'04-Uji-Halaman-29-42'!I26</f>
         <v/>
       </c>
       <c r="E37" s="13">
-        <f>'25'!H27</f>
+        <f>'04-Uji-Halaman-29-42'!I27</f>
         <v/>
       </c>
       <c r="F37" s="9" t="n"/>
@@ -8714,11 +9326,11 @@
         </is>
       </c>
       <c r="D38" s="13">
-        <f>'25'!I26</f>
+        <f>'04-Uji-Halaman-29-42'!J26</f>
         <v/>
       </c>
       <c r="E38" s="13">
-        <f>'25'!I27</f>
+        <f>'04-Uji-Halaman-29-42'!J27</f>
         <v/>
       </c>
       <c r="F38" s="9" t="n"/>
@@ -8741,11 +9353,11 @@
         </is>
       </c>
       <c r="D39" s="13">
-        <f>'25'!J26</f>
+        <f>'04-Uji-Halaman-29-42'!K26</f>
         <v/>
       </c>
       <c r="E39" s="13">
-        <f>'25'!J27</f>
+        <f>'04-Uji-Halaman-29-42'!K27</f>
         <v/>
       </c>
       <c r="F39" s="9" t="n"/>
@@ -8768,11 +9380,11 @@
         </is>
       </c>
       <c r="D40" s="13">
-        <f>'25'!K26</f>
+        <f>'04-Uji-Halaman-29-42'!L26</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>'25'!K27</f>
+        <f>'04-Uji-Halaman-29-42'!L27</f>
         <v/>
       </c>
       <c r="F40" s="9" t="n"/>
@@ -8795,11 +9407,11 @@
         </is>
       </c>
       <c r="D41" s="13">
-        <f>'25'!L26</f>
+        <f>'04-Uji-Halaman-29-42'!M26</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>'25'!L27</f>
+        <f>'04-Uji-Halaman-29-42'!M27</f>
         <v/>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -8822,11 +9434,11 @@
         </is>
       </c>
       <c r="D42" s="13">
-        <f>'25'!M26</f>
+        <f>'04-Uji-Halaman-29-42'!N26</f>
         <v/>
       </c>
       <c r="E42" s="13">
-        <f>'25'!M27</f>
+        <f>'04-Uji-Halaman-29-42'!N27</f>
         <v/>
       </c>
       <c r="F42" s="9" t="n"/>
@@ -8849,11 +9461,11 @@
         </is>
       </c>
       <c r="D43" s="13">
-        <f>'25'!N26</f>
+        <f>'04-Uji-Halaman-29-42'!O26</f>
         <v/>
       </c>
       <c r="E43" s="13">
-        <f>'25'!N27</f>
+        <f>'04-Uji-Halaman-29-42'!O27</f>
         <v/>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -8876,11 +9488,11 @@
         </is>
       </c>
       <c r="D44" s="13">
-        <f>'25'!O26</f>
+        <f>'04-Uji-Halaman-29-42'!P26</f>
         <v/>
       </c>
       <c r="E44" s="13">
-        <f>'25'!O27</f>
+        <f>'04-Uji-Halaman-29-42'!P27</f>
         <v/>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -8903,11 +9515,11 @@
         </is>
       </c>
       <c r="D45" s="13">
-        <f>'25'!P26</f>
+        <f>'04-Uji-Halaman-29-42'!Q26</f>
         <v/>
       </c>
       <c r="E45" s="13">
-        <f>'25'!P27</f>
+        <f>'04-Uji-Halaman-29-42'!Q27</f>
         <v/>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -8930,11 +9542,11 @@
         </is>
       </c>
       <c r="D46" s="13">
-        <f>'25'!C26</f>
+        <f>'05-Uji-Halaman-43-54'!D26</f>
         <v/>
       </c>
       <c r="E46" s="13">
-        <f>'25'!C27</f>
+        <f>'05-Uji-Halaman-43-54'!D27</f>
         <v/>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -8957,11 +9569,11 @@
         </is>
       </c>
       <c r="D47" s="13">
-        <f>'25'!D26</f>
+        <f>'05-Uji-Halaman-43-54'!E26</f>
         <v/>
       </c>
       <c r="E47" s="13">
-        <f>'25'!D27</f>
+        <f>'05-Uji-Halaman-43-54'!E27</f>
         <v/>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -8984,11 +9596,11 @@
         </is>
       </c>
       <c r="D48" s="13">
-        <f>'25'!E26</f>
+        <f>'05-Uji-Halaman-43-54'!F26</f>
         <v/>
       </c>
       <c r="E48" s="13">
-        <f>'25'!E27</f>
+        <f>'05-Uji-Halaman-43-54'!F27</f>
         <v/>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9011,11 +9623,11 @@
         </is>
       </c>
       <c r="D49" s="13">
-        <f>'25'!F26</f>
+        <f>'05-Uji-Halaman-43-54'!G26</f>
         <v/>
       </c>
       <c r="E49" s="13">
-        <f>'25'!F27</f>
+        <f>'05-Uji-Halaman-43-54'!G27</f>
         <v/>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9038,11 +9650,11 @@
         </is>
       </c>
       <c r="D50" s="13">
-        <f>'25'!G26</f>
+        <f>'05-Uji-Halaman-43-54'!H26</f>
         <v/>
       </c>
       <c r="E50" s="13">
-        <f>'25'!G27</f>
+        <f>'05-Uji-Halaman-43-54'!H27</f>
         <v/>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9065,11 +9677,11 @@
         </is>
       </c>
       <c r="D51" s="13">
-        <f>'25'!H26</f>
+        <f>'05-Uji-Halaman-43-54'!I26</f>
         <v/>
       </c>
       <c r="E51" s="13">
-        <f>'25'!H27</f>
+        <f>'05-Uji-Halaman-43-54'!I27</f>
         <v/>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9092,11 +9704,11 @@
         </is>
       </c>
       <c r="D52" s="13">
-        <f>'25'!I26</f>
+        <f>'05-Uji-Halaman-43-54'!J26</f>
         <v/>
       </c>
       <c r="E52" s="13">
-        <f>'25'!I27</f>
+        <f>'05-Uji-Halaman-43-54'!J27</f>
         <v/>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9119,11 +9731,11 @@
         </is>
       </c>
       <c r="D53" s="13">
-        <f>'25'!J26</f>
+        <f>'05-Uji-Halaman-43-54'!K26</f>
         <v/>
       </c>
       <c r="E53" s="13">
-        <f>'25'!J27</f>
+        <f>'05-Uji-Halaman-43-54'!K27</f>
         <v/>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -9146,11 +9758,11 @@
         </is>
       </c>
       <c r="D54" s="13">
-        <f>'25'!K26</f>
+        <f>'05-Uji-Halaman-43-54'!L26</f>
         <v/>
       </c>
       <c r="E54" s="13">
-        <f>'25'!K27</f>
+        <f>'05-Uji-Halaman-43-54'!L27</f>
         <v/>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -9173,11 +9785,11 @@
         </is>
       </c>
       <c r="D55" s="13">
-        <f>'25'!L26</f>
+        <f>'05-Uji-Halaman-43-54'!M26</f>
         <v/>
       </c>
       <c r="E55" s="13">
-        <f>'25'!L27</f>
+        <f>'05-Uji-Halaman-43-54'!M27</f>
         <v/>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -9200,11 +9812,11 @@
         </is>
       </c>
       <c r="D56" s="13">
-        <f>'25'!M26</f>
+        <f>'05-Uji-Halaman-43-54'!N26</f>
         <v/>
       </c>
       <c r="E56" s="13">
-        <f>'25'!M27</f>
+        <f>'05-Uji-Halaman-43-54'!N27</f>
         <v/>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -9227,11 +9839,11 @@
         </is>
       </c>
       <c r="D57" s="13">
-        <f>'25'!N26</f>
+        <f>'05-Uji-Halaman-43-54'!O26</f>
         <v/>
       </c>
       <c r="E57" s="13">
-        <f>'25'!N27</f>
+        <f>'05-Uji-Halaman-43-54'!O27</f>
         <v/>
       </c>
       <c r="F57" s="9" t="n"/>
